--- a/output/pdf_financials_xlsx/AVG.xlsx
+++ b/output/pdf_financials_xlsx/AVG.xlsx
@@ -1156,10 +1156,10 @@
         <v>-0.059879</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-0.362817</v>
@@ -1392,10 +1392,10 @@
         <v>-0.059879</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.362817</v>
@@ -1545,10 +1545,10 @@
         <v>-0.059879</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-1.502265</v>
@@ -1563,7 +1563,7 @@
         <v>-0.981497</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-0.362817</v>
@@ -1690,10 +1690,10 @@
         <v>1.995967</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>36.86425</v>
+        <v>-36.86425</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>47.992571</v>
+        <v>-47.992571</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>11.60204</v>
+        <v>-11.60204</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>12.0939</v>
@@ -1741,10 +1741,10 @@
         <v>-0.059879</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.362817</v>
@@ -1843,10 +1843,10 @@
         <v>-0.059879</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.362817</v>
@@ -1961,10 +1961,10 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -4652,37 +4652,37 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.062379</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.062379</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.062379</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.103795</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.778217</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.080303</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.635251</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.033015</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.161283</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.183862</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.245801</v>
       </c>
     </row>
     <row r="93">
@@ -7442,7 +7442,11 @@
           <t>Share-based payment reserve (Note 6(c))</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8716,7 +8720,11 @@
           <t>Share-based payment reserve (Note 7(c))</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -9462,7 +9470,11 @@
           <t>Share-based payment reserve (Note 8(c))</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -10454,7 +10466,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -10830,7 +10846,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -22941,10 +22961,10 @@
         <v>0.981497</v>
       </c>
       <c r="N221" s="5" t="n">
-        <v>1.740306</v>
+        <v>-1.740306</v>
       </c>
       <c r="O221" s="5" t="n">
-        <v>0.362817</v>
+        <v>-0.362817</v>
       </c>
       <c r="P221" t="inlineStr">
         <is>
@@ -31531,10 +31551,10 @@
         </is>
       </c>
       <c r="H337" s="5" t="n">
-        <v>2.94914</v>
+        <v>-2.94914</v>
       </c>
       <c r="I337" s="5" t="n">
-        <v>3.35948</v>
+        <v>-3.35948</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AVG.xlsx
+++ b/output/pdf_financials_xlsx/AVG.xlsx
@@ -2077,34 +2077,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.283947</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.231864</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.856818</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.921582</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.754186</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.927739</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>5.218564</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.265034</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.048492</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.073367</v>
@@ -2163,34 +2163,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.283947</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.231864</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.856818</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.921582</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.754186</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.927739</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>5.218564</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.265034</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.048492</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.073367</v>
@@ -2679,34 +2679,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.283947</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.246864</v>
+        <v>0.015</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.077446</v>
+        <v>0.220628</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.022699</v>
+        <v>0.101117</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.790976</v>
+        <v>0.03679</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.034795</v>
+        <v>0.107056</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>5.4105</v>
+        <v>0.191936</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.37191</v>
+        <v>0.106876</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.08619599999999999</v>
+        <v>0.037704</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.013626</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">

--- a/output/pdf_financials_xlsx/AVG.xlsx
+++ b/output/pdf_financials_xlsx/AVG.xlsx
@@ -5230,31 +5230,31 @@
         <v>-0.037083</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.435491</v>
+        <v>0.238404</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.035526</v>
+        <v>0.159075</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.01076</v>
+        <v>0.075087</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.350538</v>
+        <v>-0.420804</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.19187</v>
+        <v>0.10699</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.102529</v>
+        <v>-0.112941</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.477713</v>
+        <v>0.546885</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.176996</v>
+        <v>0.201074</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.536093</v>
+        <v>-0.538669</v>
       </c>
     </row>
     <row r="107">
@@ -5402,19 +5402,19 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.051104</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.040538</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.06536500000000001</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.072674</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.10551</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>0</v>
@@ -5423,10 +5423,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.010506</v>
       </c>
     </row>
     <row r="111">
@@ -5445,10 +5445,10 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.064458</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.114544</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -5457,7 +5457,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -5873,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -6462,10 +6462,10 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.064458</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.114544</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -6474,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.034</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -6509,10 +6509,10 @@
         <v>-0.037083</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.505912</v>
+        <v>-1.57037</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.239057</v>
+        <v>-2.353601</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-2.448202</v>
@@ -6521,7 +6521,7 @@
         <v>-1.916266</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-3.146179</v>
+        <v>-3.180179</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-3.700432</v>
@@ -11382,7 +11382,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -12152,7 +12156,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -15246,7 +15254,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19712,7 +19724,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -20326,7 +20342,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
